--- a/output/2026-09-01_22_Italia_Marche_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-01_22_Italia_Marche_Componentistica_Ventilazione_industriale.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dal 1974, impianti di aspirazione e filtrazione polveri/trucioli/nebbie oleose, sottostazioni a maniche filtranti, idrofiltri, cabine di verniciatura - system integrator B2B per conto di clienti terzi (non produttore manifatturiero che usa aspirazione internamente). Verificato su sito ufficiale e misterimprese.</t>
+          <t>Dal 1974, impianti di aspirazione e filtrazione polveri/trucioli/nebbie oleose, sottostazioni a maniche filtranti, idrofiltri, cabine di verniciatura - system integrator B2B per conto di clienti terzi (non produttore manifatturiero che usa aspirazione internamente). Verificato su sito ufficiale e misterimprese. [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40 anni di esperienza in progettazione/costruzione/installazione impianti aspirazione polveri e fumi per settori legno, meccanica, alluminio, chimica, gomma, calzaturiero, carta - system integrator B2B. Verificato su facebook, confapipesaro.eu, europages, paginegialle. Email non reperita, lasciata vuota.</t>
+          <t>40 anni di esperienza in progettazione/costruzione/installazione impianti aspirazione polveri e fumi per settori legno, meccanica, alluminio, chimica, gomma, calzaturiero, carta - system integrator B2B. Verificato su facebook, confapipesaro.eu, europages, paginegialle. Email non reperita, lasciata vuota. [DUPLICATO — vedi anche: 2026-09-01_21_Italia_Marche_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Dal 1981, progettazione/realizzazione/manutenzione impianti di filtrazione e aspirazione industriale, banchi aspiranti, sottostazioni filtranti, insonorizzazione industriale. Verificato su sito ufficiale e directory (virgilio, paginebianche, hotfrog).</t>
+          <t>Dal 1981, progettazione/realizzazione/manutenzione impianti di filtrazione e aspirazione industriale, banchi aspiranti, sottostazioni filtranti, insonorizzazione industriale. Verificato su sito ufficiale e directory (virgilio, paginebianche, hotfrog). [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Oltre 30 anni di attivita, progettazione/produzione/installazione impianti aspirazione fumi e polveri, sili metallici, sottostazioni filtranti, cicloni separatori, conformi a Direttiva Macchine 89/392/CEE. Sede indicata anche a Tavullia (PU) in alcune fonti. Verificato su sito ufficiale e directory (paginebianche, europages, marcheshopping).</t>
+          <t>Oltre 30 anni di attivita, progettazione/produzione/installazione impianti aspirazione fumi e polveri, sili metallici, sottostazioni filtranti, cicloni separatori, conformi a Direttiva Macchine 89/392/CEE. Sede indicata anche a Tavullia (PU) in alcune fonti. Verificato su sito ufficiale e directory (paginebianche, europages, marcheshopping). [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione, cappe aspiranti, tubazioni. ATTENZIONE: il target dichiarato dall'azienda e' misto ristoranti/bar/laboratori E industrie, non esclusivamente industriale - pertinenza al settore Componentistica/Ventilazione industriale solo parziale, da verificare focus specifico prima di procedere commercialmente. Verificato su sito ufficiale ed europages.</t>
+          <t>Impianti di aspirazione, cappe aspiranti, tubazioni. ATTENZIONE: il target dichiarato dall'azienda e' misto ristoranti/bar/laboratori E industrie, non esclusivamente industriale - pertinenza al settore Componentistica/Ventilazione industriale solo parziale, da verificare focus specifico prima di procedere commercialmente. Verificato su sito ufficiale ed europages. [DUPLICATO — vedi anche: 2026-09-01_21_Italia_Marche_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Rivenditore aspiratori industriali (gamma Tecnoil), compressori e impianti aria compressa/vuoto, filtrazione industriale. Confermato su sito ufficiale (proservice-srl.com). Telefono ed email non reperiti nelle fonti disponibili, lasciati vuoti.</t>
+          <t>Rivenditore aspiratori industriali (gamma Tecnoil), compressori e impianti aria compressa/vuoto, filtrazione industriale. Confermato su sito ufficiale (proservice-srl.com). Telefono ed email non reperiti nelle fonti disponibili, lasciati vuoti. [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dal 2007, impianti di ventilazione/aspirazione/condizionamento industriale; opera anche in Abruzzo (L'Aquila, Pescara, Teramo) oltre che nelle Marche (AP, MC). Verificato su sito ufficiale e directory (paginegialle).</t>
+          <t>Dal 2007, impianti di ventilazione/aspirazione/condizionamento industriale; opera anche in Abruzzo (L'Aquila, Pescara, Teramo) oltre che nelle Marche (AP, MC). Verificato su sito ufficiale e directory (paginegialle). [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Impiantistica termoidraulica/climatizzazione generalista (riscaldamento, gas, acqua, antincendio) che include anche impianti industriali di aspirazione polveri/vapori per industrie manifatturiere/plastiche/alimentari/farmaceutiche. ATTENZIONE: focus meno specialistico sulla ventilazione industriale rispetto agli altri candidati - verificare pertinenza specifica al settore. Verificato su sito ufficiale, kompass e virgilio aziende (stesso indirizzo/telefono).</t>
+          <t>Impiantistica termoidraulica/climatizzazione generalista (riscaldamento, gas, acqua, antincendio) che include anche impianti industriali di aspirazione polveri/vapori per industrie manifatturiere/plastiche/alimentari/farmaceutiche. ATTENZIONE: focus meno specialistico sulla ventilazione industriale rispetto agli altri candidati - verificare pertinenza specifica al settore. Verificato su sito ufficiale, kompass e virgilio aziende (stesso indirizzo/telefono). [DUPLICATO — vedi anche: 2026-09-01_21_Italia_Marche_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Dal 1993 (gruppo/famiglia attiva da 50 anni nel settore), progettazione/installazione/assistenza impianti aspirazione fumi e polveri secche/umide, ventilazione industriale. Verificato su sito ufficiale ed europages. Azienda familiare ma entita' giuridica distinta (indirizzo Via Forano 31/Bis e telefono propri) da Giuliodori Renzo Srl e Giuliodori Roberto Srl - NON e' un duplicato, mantenuta come riga separata.</t>
+          <t>Dal 1993 (gruppo/famiglia attiva da 50 anni nel settore), progettazione/installazione/assistenza impianti aspirazione fumi e polveri secche/umide, ventilazione industriale. Verificato su sito ufficiale ed europages. Azienda familiare ma entita' giuridica distinta (indirizzo Via Forano 31/Bis e telefono propri) da Giuliodori Renzo Srl e Giuliodori Roberto Srl - NON e' un duplicato, mantenuta come riga separata. [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Dal 1967/1968, progettazione/costruzione/installazione impianti aspirazione industriale; clienti di rilievo citati (Elica, Cucine Lube, Poltrona Frau, Baden Haus). Verificato su sito ufficiale e directory (misterimprese, prontoimprese). Entita' distinta (indirizzo Via Marconi 21 e telefono propri) da Fratelli Giuliodori Srl e Giuliodori Roberto Srl - NON e' un duplicato. Email non reperita.</t>
+          <t>Dal 1967/1968, progettazione/costruzione/installazione impianti aspirazione industriale; clienti di rilievo citati (Elica, Cucine Lube, Poltrona Frau, Baden Haus). Verificato su sito ufficiale e directory (misterimprese, prontoimprese). Entita' distinta (indirizzo Via Marconi 21 e telefono propri) da Fratelli Giuliodori Srl e Giuliodori Roberto Srl - NON e' un duplicato. Email non reperita. [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Costruzione/installazione impianti aspirazione industriale (legno, calzaturiero, meccanica, chimica, fonderie, plastica, carta, elettronica), tecnologie CAD/CAM, 30 anni di esperienza. Nessun sito web proprio individuato (presenza solo su kompass e paginebianche), campo sito_web lasciato vuoto. Entita' distinta (indirizzo Via Marconi 59 e telefono propri) da Fratelli Giuliodori Srl e Giuliodori Renzo Srl - NON e' un duplicato.</t>
+          <t>Costruzione/installazione impianti aspirazione industriale (legno, calzaturiero, meccanica, chimica, fonderie, plastica, carta, elettronica), tecnologie CAD/CAM, 30 anni di esperienza. Nessun sito web proprio individuato (presenza solo su kompass e paginebianche), campo sito_web lasciato vuoto. Entita' distinta (indirizzo Via Marconi 59 e telefono propri) da Fratelli Giuliodori Srl e Giuliodori Renzo Srl - NON e' un duplicato. [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
